--- a/artfynd/A 53180-2025 artfynd.xlsx
+++ b/artfynd/A 53180-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688685</v>
       </c>
       <c r="B2" t="n">
-        <v>80176</v>
+        <v>80180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129688684</v>
       </c>
       <c r="B3" t="n">
-        <v>80176</v>
+        <v>80180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129688668</v>
       </c>
       <c r="B4" t="n">
-        <v>80176</v>
+        <v>80180</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 53180-2025 artfynd.xlsx
+++ b/artfynd/A 53180-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688685</v>
       </c>
       <c r="B2" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129688684</v>
       </c>
       <c r="B3" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129688668</v>
       </c>
       <c r="B4" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 53180-2025 artfynd.xlsx
+++ b/artfynd/A 53180-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688685</v>
       </c>
       <c r="B2" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129688684</v>
       </c>
       <c r="B3" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129688668</v>
       </c>
       <c r="B4" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 53180-2025 artfynd.xlsx
+++ b/artfynd/A 53180-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688685</v>
       </c>
       <c r="B2" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129688684</v>
       </c>
       <c r="B3" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129688668</v>
       </c>
       <c r="B4" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 53180-2025 artfynd.xlsx
+++ b/artfynd/A 53180-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688685</v>
       </c>
       <c r="B2" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129688684</v>
       </c>
       <c r="B3" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129688668</v>
       </c>
       <c r="B4" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 53180-2025 artfynd.xlsx
+++ b/artfynd/A 53180-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688685</v>
       </c>
       <c r="B2" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129688684</v>
       </c>
       <c r="B3" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129688668</v>
       </c>
       <c r="B4" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 53180-2025 artfynd.xlsx
+++ b/artfynd/A 53180-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688685</v>
       </c>
       <c r="B2" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129688684</v>
       </c>
       <c r="B3" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129688668</v>
       </c>
       <c r="B4" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 53180-2025 artfynd.xlsx
+++ b/artfynd/A 53180-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688685</v>
       </c>
       <c r="B2" t="n">
-        <v>80194</v>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129688684</v>
+        <v>129688668</v>
       </c>
       <c r="B3" t="n">
-        <v>80194</v>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>764237</v>
+        <v>764296</v>
       </c>
       <c r="R3" t="n">
-        <v>7330554</v>
+        <v>7330542</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,12 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129688668</v>
+        <v>129688683</v>
       </c>
       <c r="B4" t="n">
-        <v>80194</v>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>764296</v>
+        <v>764237</v>
       </c>
       <c r="R4" t="n">
-        <v>7330542</v>
+        <v>7330554</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -956,12 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 53180-2025 artfynd.xlsx
+++ b/artfynd/A 53180-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129688668</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129688683</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,8 +1005,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129688685</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>